--- a/output_categorized.xlsx
+++ b/output_categorized.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,21 +509,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6044588</v>
+        <v>6750618</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BM-00105045</t>
+          <t>BM-00103425</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -531,79 +531,79 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-08-2025</t>
+          <t>10-03-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14-04-2026</t>
+          <t>14-05-2026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>23.25</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>21.5</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6932046</v>
+        <v>6667389</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+          <t>BM-00094172</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Xue Zhenyu (VM/ESC-AU)</t>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>175000</v>
+        <v>50000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23-04-2026</t>
+          <t>11-02-2026</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>27-05-2026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.52</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.52</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -635,21 +635,21 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6701983</v>
+        <v>6318896</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>| 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+          <t>BM-00108205</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Xue Zhenyu (VM/ESC-AU)</t>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -657,43 +657,4071 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>04-11-2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6210982</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>09-10-2025</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>43</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>43</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6195643</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01-10-2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>55</v>
+      </c>
+      <c r="P6" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6172585</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BM-00102067</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>24-09-2025</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>17</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6079924</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BM-00103221</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>27-08-2025</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>21-10-2025</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6063624</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>22-08-2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6044649</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14-08-2025</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6044647</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>14-08-2025</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6044588</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>14-08-2025</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>14-04-2026</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6044570</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>14-08-2025</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22-07-2026</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1072.28</v>
+      </c>
+      <c r="J13" t="n">
+        <v>305.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1377.73</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1399.23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6028762</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BM-00090913</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>11-08-2025</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>31-10-2025</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6002206</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>01-08-2025</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>03-09-2025</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5977873</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BM-00094172</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>25-07-2025</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>18-08-2025</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5938012</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>56</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5938010</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>180</v>
+      </c>
+      <c r="I18" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>180</v>
+      </c>
+      <c r="L18" t="n">
+        <v>146</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>118.84</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>118.84</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>264.84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5938008</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="J19" t="n">
+        <v>30</v>
+      </c>
+      <c r="K19" t="n">
+        <v>229</v>
+      </c>
+      <c r="L19" t="n">
+        <v>246.84</v>
+      </c>
+      <c r="M19" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>257.17</v>
+      </c>
+      <c r="O19" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>513.67</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>760.51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5938002</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>16-01-2026</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5925507</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BM-00091219</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gouwens Vicki (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10-07-2025</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>24</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5806348</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BM-00096778</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>09-06-2025</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>10-12-2025</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>41</v>
+      </c>
+      <c r="I22" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>41</v>
+      </c>
+      <c r="L22" t="n">
+        <v>34</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5770927</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>28-05-2025</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>19-06-2025</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5757449</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BM-00101235</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>25-05-2025</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2455.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2455.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>108.83</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>108.83</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>111.83</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5757447</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BM-00101235</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>25-05-2025</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5735436</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BM-00102067</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>19-05-2025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>24-09-2025</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>37</v>
+      </c>
+      <c r="J26" t="n">
+        <v>62</v>
+      </c>
+      <c r="K26" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>99</v>
+      </c>
+      <c r="M26" t="n">
+        <v>42</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5722826</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14-05-2025</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>04-06-2025</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5691189</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BM-00096859</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gouwens Vicki (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>05-05-2025</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>601.75</v>
+      </c>
+      <c r="I28" t="n">
+        <v>37</v>
+      </c>
+      <c r="J28" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>601.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5676413</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BM-00094172</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>28-04-2025</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>162</v>
+      </c>
+      <c r="I29" t="n">
+        <v>23</v>
+      </c>
+      <c r="J29" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="K29" t="n">
+        <v>162</v>
+      </c>
+      <c r="L29" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>119.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5650491</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BM-00101235</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>17-04-2025</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>17-01-2026</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5650429</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BM-00081137</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>17-04-2025</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5643981</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BM-00090913</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>16-04-2025</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>11-11-2025</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>34</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5633954</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BM-00081137</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>14-04-2025</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5621126</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BM-00103221</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>09-04-2025</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>18-06-2025</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>11</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>12</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5606504</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BM-00103221</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>07-04-2025</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>04-11-2025</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="O35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>85.81999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5589702</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BM-00105045</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>01-04-2025</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>21-10-2025</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>331.15</v>
+      </c>
+      <c r="I36" t="n">
+        <v>451.33</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1549.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2000.83</v>
+      </c>
+      <c r="M36" t="n">
+        <v>32</v>
+      </c>
+      <c r="N36" t="n">
+        <v>140.08</v>
+      </c>
+      <c r="O36" t="n">
+        <v>27</v>
+      </c>
+      <c r="P36" t="n">
+        <v>167.08</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2167.91</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5587328</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BM-00102067</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>01-04-2025</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>12-08-2025</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>129</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>27</v>
+      </c>
+      <c r="P37" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5571537</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gouwens Vicki (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>27-03-2025</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5543806</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>20-03-2025</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>23</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>21</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5528829</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BM-00047410</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>17-03-2025</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12-08-2025</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>45</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>45</v>
+      </c>
+      <c r="M40" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5527537</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BM-00096778</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>17-03-2025</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>09-06-2025</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>20</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>20</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5490259</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BM-00101235</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>05-03-2025</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="J42" t="n">
+        <v>574.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>159</v>
+      </c>
+      <c r="L42" t="n">
+        <v>782.55</v>
+      </c>
+      <c r="M42" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>245.75</v>
+      </c>
+      <c r="O42" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="P42" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1074.55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5456353</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BM-00096778</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>25-02-2025</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>29-07-2025</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>30</v>
+      </c>
+      <c r="K43" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>30</v>
+      </c>
+      <c r="M43" t="n">
+        <v>71</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>52</v>
+      </c>
+      <c r="P43" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5407094</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BM-00101235</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11-02-2025</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>900.4299999999999</v>
+      </c>
+      <c r="J44" t="n">
+        <v>450</v>
+      </c>
+      <c r="K44" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1350.43</v>
+      </c>
+      <c r="M44" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>511.12</v>
+      </c>
+      <c r="O44" t="n">
+        <v>257.9</v>
+      </c>
+      <c r="P44" t="n">
+        <v>769.02</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2119.44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5402008</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BM-00091219</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10-02-2025</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10-02-2025</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5366157</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BM-00103221</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>28-01-2025</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>06-06-2025</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5355943</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BM-00081137</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>24-01-2025</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5312810</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BM-00080788</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>08-01-2025</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>13</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K48" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M48" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5305988</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BM-00096778</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>07-01-2025</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>29-07-2025</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>103</v>
+      </c>
+      <c r="K49" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>17</v>
+      </c>
+      <c r="N49" t="n">
+        <v>39</v>
+      </c>
+      <c r="O49" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="P49" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5305839</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BM-00096778</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>07-01-2025</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>12-08-2025</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>17</v>
+      </c>
+      <c r="I50" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L50" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6932046</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>23-04-2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6932013</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>23-04-2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>03-07-2026</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6750604</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10-03-2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6701983</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>26-02-2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>26-03-2026</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6659467</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>09-02-2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6269204</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>23-10-2025</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>36</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L56" t="n">
+        <v>39</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6269200</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>23-10-2025</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>13-05-2026</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6211015</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>09-10-2025</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>18-12-2025</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5926884</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>11-07-2025</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>13-05-2026</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5926478</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>11-07-2025</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>12-08-2025</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>7</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5861140</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>25-06-2025</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="O61" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="P61" t="n">
+        <v>104.92</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>104.92</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5767229</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>28-05-2025</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>13-05-2026</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5715690</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>13-05-2025</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>6</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5715685</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>13-05-2025</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>11-07-2025</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>5673425</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>28-04-2025</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>29-05-2025</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5634293</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>15-04-2025</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>12-06-2025</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>5470646</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>28-02-2025</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>450.6</v>
+      </c>
+      <c r="I67" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34</v>
+      </c>
+      <c r="K67" t="n">
+        <v>612.6</v>
+      </c>
+      <c r="L67" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="M67" t="n">
+        <v>162</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" t="n">
+        <v>82</v>
+      </c>
+      <c r="P67" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>190.32</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5439257</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20-02-2025</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20-03-2025</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>4</v>
+      </c>
+      <c r="K68" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M68" t="n">
+        <v>91</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -707,7 +4735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,7 +4773,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PM Interface Element ID</t>
+          <t>BM_ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -907,172 +4935,1586 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.52</v>
+        <v>557.6600000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>115.82</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>0.52</v>
+        <v>810.66</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>199.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>61.17</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>178.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>239.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>439.74</v>
       </c>
       <c r="R3" t="n">
-        <v>583.33</v>
+        <v>909394.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>493298.08</v>
       </c>
       <c r="T3" t="n">
-        <v>583.33</v>
+        <v>625580.13</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>224157.05</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>283814.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>269141.03</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>64.83%</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>35.17%</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6044588</v>
+        <v>5528829</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>BM-00047410</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17-03-2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>12-08-2025</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>45</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>45</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3044.87</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14423.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14423.08</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3044.87</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>17.43%</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>82.57%</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5312810</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BM-00080788</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-01-2025</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>107131.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6450.32</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14583.33</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6450.32</v>
+      </c>
+      <c r="V5" t="n">
+        <v>92548.08</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>94.32%</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5650429</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BM-00081137</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>17-04-2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6028762</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BM-00090913</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11-08-2025</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>31-10-2025</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1282.05</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16185.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1282.05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>16185.9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7.34%</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>92.66%</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5925507</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BM-00091219</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gouwens Vicki (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10-07-2025</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>26923.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>18509.62</v>
+      </c>
+      <c r="T8" t="n">
+        <v>26923.08</v>
+      </c>
+      <c r="U8" t="n">
+        <v>18509.62</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>59.26%</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>40.74%</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6667389</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BM-00094172</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vijayanand Sivakumar (MS/ECV-DX2-XC)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11-02-2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>166</v>
+      </c>
+      <c r="I9" t="n">
+        <v>27</v>
+      </c>
+      <c r="J9" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>166</v>
+      </c>
+      <c r="L9" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>53205.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>44951.92</v>
+      </c>
+      <c r="T9" t="n">
+        <v>53205.13</v>
+      </c>
+      <c r="U9" t="n">
+        <v>44951.92</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5806348</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BM-00096778</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>09-06-2025</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10-12-2025</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>198</v>
+      </c>
+      <c r="I10" t="n">
+        <v>198</v>
+      </c>
+      <c r="J10" t="n">
+        <v>196</v>
+      </c>
+      <c r="K10" t="n">
+        <v>286</v>
+      </c>
+      <c r="L10" t="n">
+        <v>394</v>
+      </c>
+      <c r="M10" t="n">
+        <v>88</v>
+      </c>
+      <c r="N10" t="n">
+        <v>39</v>
+      </c>
+      <c r="O10" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>91666.67</v>
+      </c>
+      <c r="S10" t="n">
+        <v>192147.44</v>
+      </c>
+      <c r="T10" t="n">
+        <v>63461.54</v>
+      </c>
+      <c r="U10" t="n">
+        <v>126282.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>28205.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>65865.38</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>32.3%</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>67.7%</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5691189</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BM-00096859</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gouwens Vicki (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>05-05-2025</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>06-01-2026</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>601.75</v>
+      </c>
+      <c r="I11" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>601.75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>88</v>
+      </c>
+      <c r="R11" t="n">
+        <v>675040.0600000001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>98717.95</v>
+      </c>
+      <c r="T11" t="n">
+        <v>675040.0600000001</v>
+      </c>
+      <c r="U11" t="n">
+        <v>67868.59</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>30849.36</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>87.24%</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>12.76%</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5757449</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BM-00101235</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Saleem Shaheed (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25-05-2025</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2694.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1111.68</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1024.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3167.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2135.98</v>
+      </c>
+      <c r="M12" t="n">
+        <v>472.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>865.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>304.15</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1169.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3305.82</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3552836.54</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3708451.92</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3022339.74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2396131.41</v>
+      </c>
+      <c r="V12" t="n">
+        <v>530496.79</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1312331.73</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>48.93%</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>51.07%</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6172585</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BM-00102067</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D_Nirmala Vijayabaskar (MS/EBN-AFO-VM)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>24-09-2025</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>58</v>
+      </c>
+      <c r="I13" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>104</v>
+      </c>
+      <c r="L13" t="n">
+        <v>282</v>
+      </c>
+      <c r="M13" t="n">
+        <v>46</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>318</v>
+      </c>
+      <c r="R13" t="n">
+        <v>33333.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>101923.08</v>
+      </c>
+      <c r="T13" t="n">
+        <v>18589.74</v>
+      </c>
+      <c r="U13" t="n">
+        <v>90384.62</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14743.59</v>
+      </c>
+      <c r="W13" t="n">
+        <v>11538.46</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>24.64%</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>75.36%</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6079924</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BM-00103221</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>27-08-2025</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>21-10-2025</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="O14" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>142.32</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>165.82</v>
+      </c>
+      <c r="R14" t="n">
+        <v>45432.69</v>
+      </c>
+      <c r="S14" t="n">
+        <v>186016.03</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4487.18</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26362.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>40945.51</v>
+      </c>
+      <c r="W14" t="n">
+        <v>159653.85</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>19.63%</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>80.37%</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6750618</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Xue Zhenyu (VM/ESC-AU)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10-03-2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>14-05-2026</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>47</v>
+      </c>
+      <c r="I15" t="n">
+        <v>43</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>135</v>
+      </c>
+      <c r="R15" t="n">
+        <v>79254.81</v>
+      </c>
+      <c r="S15" t="n">
+        <v>151442.31</v>
+      </c>
+      <c r="T15" t="n">
+        <v>52724.36</v>
+      </c>
+      <c r="U15" t="n">
+        <v>61137.82</v>
+      </c>
+      <c r="V15" t="n">
+        <v>26530.45</v>
+      </c>
+      <c r="W15" t="n">
+        <v>90304.49000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>34.35%</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>65.65%</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>75.44%</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>75.63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6002206</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BM-00103425</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>01-08-2025</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>03-09-2025</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>25801.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>48798.08</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2243.59</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>23557.69</v>
+      </c>
+      <c r="W16" t="n">
+        <v>48798.08</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>65.41%</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>24.56%</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>24.37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6044649</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>BM-00105045</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ahmed Khuddus Jameel (VM/EFO1)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>North America</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E17" t="n">
         <v>175000</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>14-08-2025</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>14-04-2026</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>26081.73</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25240.38</v>
-      </c>
-      <c r="T4" t="n">
-        <v>7291.67</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1121.79</v>
-      </c>
-      <c r="V4" t="n">
-        <v>18790.06</v>
-      </c>
-      <c r="W4" t="n">
-        <v>24118.59</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>50.82%</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>49.18%</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="H17" t="n">
+        <v>812.15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1796.95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1975.45</v>
+      </c>
+      <c r="K17" t="n">
+        <v>955.15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3772.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>143</v>
+      </c>
+      <c r="N17" t="n">
+        <v>572.09</v>
+      </c>
+      <c r="O17" t="n">
+        <v>326.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>898.59</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4670.99</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1071482.37</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5239892.63</v>
+      </c>
+      <c r="T17" t="n">
+        <v>911065.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4231858.97</v>
+      </c>
+      <c r="V17" t="n">
+        <v>160416.67</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1008033.65</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>16.98%</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>83.02%</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6318896</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BM-00108205</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rajaretnam Anandbabu (VM/EFO1)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>04-11-2025</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>24971.15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>24971.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>

--- a/output_categorized.xlsx
+++ b/output_categorized.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Original Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aggregated Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +47,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,53 +508,51 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>6044588</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7135341</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BM-00105045</t>
+          <t>BM-00105824</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Teran Quintanilla Enrique (BGSW/ECC2.4-MS)</t>
+          <t>Kim Na Kyong (VM/ESP1-BR)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72727</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-08-2025</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14-04-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -559,164 +561,158 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6044588</t>
-        </is>
+      <c r="A3" t="n">
+        <v>7119921</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BM-00105045</t>
+          <t>BM-00105824</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Venkatesan Ravi (MS/EFO42-VM)</t>
+          <t>Glitz Ute (VM/ECE1-CB)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14-06-2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6806310</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anant R K Ashwin (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>50000</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>14-08-2025</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>14-04-2026</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6044588</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BM-00105045</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bhatia Tanmay (VM/ESC-AU)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>175000</v>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14-08-2025</t>
+          <t>23-03-2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-04-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.5</v>
+        <v>1001.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>673.3</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>199.45</v>
       </c>
       <c r="K4" t="n">
-        <v>6.5</v>
+        <v>1052.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>872.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>43.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>916.05</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6932046</t>
-        </is>
+      <c r="A5" t="n">
+        <v>6806310</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+          <t>BM-00105824</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tan Terence (VM/ESC-AU)</t>
+          <t>Heid Dimitrij (VM/ESB4)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -724,28 +720,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23-04-2026</t>
+          <t>23-03-2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.52</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>88.25</v>
       </c>
       <c r="K5" t="n">
-        <v>0.52</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>88.25</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -760,75 +756,6527 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>88.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6701983</t>
-        </is>
+      <c r="A6" t="n">
+        <v>6806310</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>| 11 | Official_SW_Plan_Draft_1388451_Read.mpp | {51d59cf1-4fa9-ea11-ae83-e4a471593ba6} | 2.1.9</t>
+          <t>BM-00105824</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xue Zhenyu (VM/ESC-AU)</t>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>24-07-2026</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6806300</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>175000</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>26-02-2026</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>26-03-2026</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10-07-2026</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41</v>
+      </c>
+      <c r="K7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>41</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6806300</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rukhsana Tabassum (MS/EBV5-SWC)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10-07-2026</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>552.85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>315.65</v>
+      </c>
+      <c r="J8" t="n">
+        <v>244.75</v>
+      </c>
+      <c r="K8" t="n">
+        <v>557.85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>560.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>616.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6806296</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Adithya Krishnan (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>494.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>661.0700000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>741.3200000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>741.3200000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6806296</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>To Giang Tuan Anh (MS/EHV12-VM)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>42545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>170.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6806296</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>198.13</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>198.13</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>198.13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6806289</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kanaga Durga Deenadayalan (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1201.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>893.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>445</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2095.7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2144.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6806289</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Elamari Taoufik (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>54</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>480.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>480.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>480.45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6806283</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Athiyaman Subramaniam (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>430</v>
+      </c>
+      <c r="I14" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>252.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>451</v>
+      </c>
+      <c r="L14" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>432.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6806283</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>154.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6806283</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lima Rui (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6394459</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Adithya Krishnan (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>213.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>324.75</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>334.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6394459</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gaertner Sebastian (VM/ESB2)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>19-05-2026</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11</v>
+      </c>
+      <c r="L18" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>185.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6394456</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Harmain Atufa (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>02-04-2026</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>238.25</v>
+      </c>
+      <c r="I19" t="n">
+        <v>246.65</v>
+      </c>
+      <c r="J19" t="n">
+        <v>497.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>259.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>744.1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>750.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6394456</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Shibu Rohan Joseph (VM/ESC1)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>02-04-2026</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6394456</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>02-04-2026</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="L21" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="M21" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>104.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6394454</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ravi Ranjan Kishor (VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6394454</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Anirudhra C S (MS/EBD11-VM)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>284</v>
+      </c>
+      <c r="I23" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>291</v>
+      </c>
+      <c r="L23" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>23</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>363.35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6394454</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6394452</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar Nagaraj (MS/EBV5-SWC)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10-03-2026</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>277</v>
+      </c>
+      <c r="J25" t="n">
+        <v>69</v>
+      </c>
+      <c r="K25" t="n">
+        <v>249.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>346</v>
+      </c>
+      <c r="M25" t="n">
+        <v>31</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6394452</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brueggemann Joerg (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10-03-2026</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6394452</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19-11-2025</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10-03-2026</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>136.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6259964</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar Nagaraj (MS/EBV5-SWC)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20-10-2025</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>12-02-2026</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>472.65</v>
+      </c>
+      <c r="J28" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>634.15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>637.35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6259964</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lima Rui (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>20-10-2025</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>12-02-2026</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6259964</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gaertner Sebastian (VM/ESB2)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20-10-2025</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>12-02-2026</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>41</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12</v>
+      </c>
+      <c r="K30" t="n">
+        <v>41</v>
+      </c>
+      <c r="L30" t="n">
+        <v>12</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6229262</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ouhmayd Adil (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>14-10-2025</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>18-12-2025</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>18</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6229262</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sarath Kumar M Sasidharan (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>14-10-2025</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>18-12-2025</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>19</v>
+      </c>
+      <c r="L32" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>130.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6229251</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arunkumar Eswaran (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>14-10-2025</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>09-12-2025</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>60</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>16</v>
+      </c>
+      <c r="L33" t="n">
+        <v>60</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6229251</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ouhmayd Adil (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>14-10-2025</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>09-12-2025</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5936942</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gokul Ramachandran (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>113</v>
+      </c>
+      <c r="I35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>113</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5936942</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>105</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>105</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5936937</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Adithya Krishnan (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>225.75</v>
+      </c>
+      <c r="I37" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>225.75</v>
+      </c>
+      <c r="L37" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5936933</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lima Rui (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>05-10-2025</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>11</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5936930</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ouhmayd Adil (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>14-07-2025</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>15-09-2025</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5680836</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>28.31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5680836</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gyajangi Sai Ramana (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>806.7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1306.85</v>
+      </c>
+      <c r="J41" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>821.3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1677.25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1698.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5680836</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="K42" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>22.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5680821</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Kanaga Durga Deenadayalan (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>513.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>518.1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>381.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5680821</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="K44" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>78.95</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5680821</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Elamari Taoufik (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>264.8</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>74</v>
+      </c>
+      <c r="K45" t="n">
+        <v>341</v>
+      </c>
+      <c r="L45" t="n">
+        <v>74</v>
+      </c>
+      <c r="M45" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5680812</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Susan Philip Deenu (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>23-02-2026</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>214.75</v>
+      </c>
+      <c r="I46" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>217.25</v>
+      </c>
+      <c r="L46" t="n">
+        <v>141</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5680812</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>23-02-2026</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5680783</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar Nagaraj (MS/EBV5-SWC)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>164.95</v>
+      </c>
+      <c r="I48" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="J48" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>204.1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="M48" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>147.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5680783</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lima Rui (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>16</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>16</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5680783</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ravi Ranjan Kishor (VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>06-02-2026</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>11</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="L50" t="n">
+        <v>11</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5680769</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Arunkumar Eswaran (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>24-11-2025</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>134</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>180</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>46</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5680769</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>24-11-2025</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5680765</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Gyajangi Sai Ramana (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>09-12-2025</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="L53" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>393.55</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5680765</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Reznikov Vladyslav (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>09-12-2025</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>20</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>20</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5680765</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ouhmayd Adil (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>09-12-2025</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5680760</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Anant R K Ashwin (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="I56" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="L56" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="M56" t="n">
+        <v>10</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>142.7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5680760</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Elamari Taoufik (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>30</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5680760</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Lima Rui (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>37</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>37</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5680751</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Adithya Krishnan (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5680751</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ouhmayd Adil (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>23</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>31</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>8</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5680742</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Anant R K Ashwin (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>164</v>
+      </c>
+      <c r="I61" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="J61" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>164</v>
+      </c>
+      <c r="L61" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>372.74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5680742</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Elamari Taoufik (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>171</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>171</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5680742</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Lima Rui (VM/ESE1-Brg)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>29-04-2025</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>22-10-2025</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>12</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>12</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7085299</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Anitha Anju (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>13-07-2026</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>25</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>25</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="P64" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>48.75</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6920251</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Jeyshree G M P (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>21-04-2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>22-05-2026</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>12</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>12</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6618848</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Abishek Boraian (MS/EMB1-VM)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>29-01-2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>29-01-2026</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6516864</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Angadi Darshan Amaresh (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>25-12-2025</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>603.85</v>
+      </c>
+      <c r="I67" t="n">
+        <v>722.35</v>
+      </c>
+      <c r="J67" t="n">
+        <v>437.45</v>
+      </c>
+      <c r="K67" t="n">
+        <v>827.85</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1159.8</v>
+      </c>
+      <c r="M67" t="n">
+        <v>224</v>
+      </c>
+      <c r="N67" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="P67" t="n">
+        <v>228.85</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1388.65</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6516864</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EXTERNAL Bousnina Mohamed (TS, VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>25-12-2025</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6516864</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EXTERNAL Balakrishnan Vengatesh (Technology and Strategy (TS), VM/ECE2-CB)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>25-12-2025</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6436546</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BM-00076075</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Snehaa Asokan (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>13-02-2026</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>135</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>135</v>
+      </c>
+      <c r="L70" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="P70" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>5833959</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BM-00076075</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Majhi Shouvik (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>18-06-2025</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>18-07-2025</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>42</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5579753</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BM-00076075</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Majhi Shouvik (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>31-03-2025</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>22-05-2026</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="I72" t="n">
+        <v>584</v>
+      </c>
+      <c r="J72" t="n">
+        <v>398</v>
+      </c>
+      <c r="K72" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="L72" t="n">
+        <v>982</v>
+      </c>
+      <c r="M72" t="n">
+        <v>100</v>
+      </c>
+      <c r="N72" t="n">
+        <v>384.25</v>
+      </c>
+      <c r="O72" t="n">
+        <v>357</v>
+      </c>
+      <c r="P72" t="n">
+        <v>741.25</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1723.25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>5579746</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BM-00076075</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Jeyshree G M P (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>31-03-2025</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>16-12-2025</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>632.2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2109.9</v>
+      </c>
+      <c r="K73" t="n">
+        <v>992.2</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2645.4</v>
+      </c>
+      <c r="M73" t="n">
+        <v>360</v>
+      </c>
+      <c r="N73" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="O73" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="P73" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2965.4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>5500149</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Anitha Anju (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>06-04-2026</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>892.1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>439.5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>906.5</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1155.85</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1346</v>
+      </c>
+      <c r="M74" t="n">
+        <v>263.75</v>
+      </c>
+      <c r="N74" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="O74" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="P74" t="n">
+        <v>318.25</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1664.25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>5500149</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>EXTERNAL Balakrishnan Vengatesh (Technology and Strategy (TS), VM/ECE2-CB)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>06-04-2026</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>57</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>5500149</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>EXTERNAL Bousnina Mohamed (TS, VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>06-04-2026</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>19</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P76" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>53.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>5500147</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Lakkoju Veera Venkata Naga Sri Charan (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="I77" t="n">
+        <v>55</v>
+      </c>
+      <c r="J77" t="n">
+        <v>372</v>
+      </c>
+      <c r="K77" t="n">
+        <v>482</v>
+      </c>
+      <c r="L77" t="n">
+        <v>427</v>
+      </c>
+      <c r="M77" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="N77" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>476.25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>5500147</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tran Le Hoang (MS/EHV12-VM)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>42545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>38</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>38</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>5500147</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EXTERNAL Balakrishnan Vengatesh (Technology and Strategy (TS), VM/ECE2-CB)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>36</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>36</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>108.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>5500147</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EXTERNAL Bousnina Mohamed (TS, VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>24</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>24</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>5500145</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Adithya Krishnan (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>12-09-2025</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>610.45</v>
+      </c>
+      <c r="I81" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="J81" t="n">
+        <v>781.7</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1003.75</v>
+      </c>
+      <c r="L81" t="n">
+        <v>945.2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="O81" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="P81" t="n">
+        <v>238.05</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1183.25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>5500145</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EXTERNAL Besson Lucas (TS, VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>12-09-2025</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>9</v>
+      </c>
+      <c r="J82" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="P82" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>142.05</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>5500145</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EXTERNAL Balakrishnan Vengatesh (Technology and Strategy (TS), VM/ECE2-CB)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>12-09-2025</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>5500143</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Singamsetty Vandana (MS/EBV3-SWC)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>09-09-2025</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1266.45</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1264.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>902.6</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1351.45</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2167.2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>85</v>
+      </c>
+      <c r="N84" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="O84" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="P84" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>5500143</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EXTERNAL Bousnina Mohamed (TS, VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>09-09-2025</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="J85" t="n">
+        <v>561.3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>677.45</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="O85" t="n">
+        <v>75</v>
+      </c>
+      <c r="P85" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>768.7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>5500143</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EXTERNAL Balakrishnan Vengatesh (Technology and Strategy (TS), VM/ECE2-CB)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>09-09-2025</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>148.15</v>
+      </c>
+      <c r="J86" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>6</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>168.65</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>5417327</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BM-00087996</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Abishek K S D (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>13-02-2025</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>233</v>
+      </c>
+      <c r="I87" t="n">
+        <v>738.65</v>
+      </c>
+      <c r="J87" t="n">
+        <v>664.75</v>
+      </c>
+      <c r="K87" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1403.4</v>
+      </c>
+      <c r="M87" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="O87" t="n">
+        <v>164</v>
+      </c>
+      <c r="P87" t="n">
+        <v>229.25</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1632.65</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>5417327</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BM-00087996</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXTERNAL Ramamurthy Ragavi (T&amp;amp;S (Technology and Strategy), VM/ESB3-CB)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>13-02-2025</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>119</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>30</v>
+      </c>
+      <c r="O88" t="n">
+        <v>14</v>
+      </c>
+      <c r="P88" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>308.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Actual (ALM)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Development Cost (ALM)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Rework Cost (ALM)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Component Contribution (ALM)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Region Contribution (ALM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BM_ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Owner Details</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Rate Card (€)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Resolution Date</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NET_DEV (Hours)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DCOM_DEV (Hours)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DSM_DEV (Hours)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NET_FINAL (Hours)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DCOM_DSM_DEV (Hours)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NET_Rework (Hours)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>DCOM_Rework (Hours)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>DSM_Rework (Hours)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DCOM_DSM_REWORK_TOTAL (Hours)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>DCOM_DSM_FINAL (Hours)</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>DCOM&amp;DSM</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DCOM&amp;DSM</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>DCOM&amp;DSM</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>DCOM&amp;DSM</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>DCOM&amp;DSM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6516864</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EXTERNAL Bousnina Mohamed (TS, VM/ESB3)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>25-12-2025</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>125.15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>815.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>940.3000000000001</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1080.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5608.97</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1212099.36</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5608.97</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1054823.72</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>157275.64</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>99.54%</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>34.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7085299</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anitha Anju (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>03-06-2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13-07-2026</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3763.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2647.45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3400.25</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4845.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6047.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1082.3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>683</v>
+      </c>
+      <c r="O4" t="n">
+        <v>326.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1009.45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7057.15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1553173.08</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2261907.05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1206282.05</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1938365.38</v>
+      </c>
+      <c r="V4" t="n">
+        <v>346891.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>323541.67</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>40.71%</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>59.29%</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>99.64%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>64.92%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6516864</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EXTERNAL Balakrishnan Vengatesh (Technology and Strategy (TS), VM/ECE2-CB)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25-12-2025</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>30-05-2026</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>428.65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5500147</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BM-00068408</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tran Le Hoang (MS/EHV12-VM)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>07-03-2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>38</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10363.53</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>10363.53</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6436546</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BM-00076075</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Snehaa Asokan (MS/EHE11-VM)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>02-12-2025</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>13-02-2026</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1049.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1204</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2613.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1509.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3817.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>460</v>
+      </c>
+      <c r="N7" t="n">
+        <v>529.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>574</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1103.75</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4921.15</v>
+      </c>
+      <c r="R7" t="n">
+        <v>483910.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1577291.67</v>
+      </c>
+      <c r="T7" t="n">
+        <v>336474.36</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1223525.64</v>
+      </c>
+      <c r="V7" t="n">
+        <v>147435.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>353766.03</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>23.48%</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>76.52%</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5417327</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BM-00087996</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EXTERNAL Ramamurthy Ragavi (T&amp;amp;S (Technology and Strategy), VM/ESB3-CB)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13-02-2025</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>119</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>346073.72</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>296714.74</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>49358.97</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>39.81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5417327</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BM-00087996</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Abishek K S D (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13-02-2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>233</v>
+      </c>
+      <c r="I9" t="n">
+        <v>738.65</v>
+      </c>
+      <c r="J9" t="n">
+        <v>664.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1403.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>164</v>
+      </c>
+      <c r="P9" t="n">
+        <v>229.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1632.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>101762.82</v>
+      </c>
+      <c r="S9" t="n">
+        <v>523285.26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>74679.49000000001</v>
+      </c>
+      <c r="U9" t="n">
+        <v>449807.69</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27083.33</v>
+      </c>
+      <c r="W9" t="n">
+        <v>73477.56</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>16.28%</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>83.72%</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>60.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6806310</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Heid Dimitrij (VM/ESB4)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>175000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>24-07-2026</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1025.85</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1412.33</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1329.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1437.33</v>
+      </c>
+      <c r="M10" t="n">
+        <v>303.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1444.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1491370.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1620241.99</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1150793.27</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1612389.42</v>
+      </c>
+      <c r="V10" t="n">
+        <v>340576.92</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7852.56</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>47.93%</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>52.07%</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>39.03%</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>31.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6806310</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Anant R K Ashwin (MS/EHE2-VM)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>24-07-2026</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6942.85</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7017.41</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3544.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7267.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10562.21</v>
+      </c>
+      <c r="M11" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="O11" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>257.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10819.41</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2329455.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3467759.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2225272.44</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3385323.72</v>
+      </c>
+      <c r="V11" t="n">
+        <v>104182.69</v>
+      </c>
+      <c r="W11" t="n">
+        <v>82435.89999999999</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>40.18%</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>59.82%</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>60.97%</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>67.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7135341</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kim Na Kyong (VM/ESP1-BR)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>632.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>632.96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>637.96</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6806296</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BM-00105824</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>To Giang Tuan Anh (MS/EHV12-VM)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>46499.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>46499.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="R1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>